--- a/Verification/Officer_Verification_Dashboard.xlsx
+++ b/Verification/Officer_Verification_Dashboard.xlsx
@@ -11,181 +11,560 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Numeric ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Numeric ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Text</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Text</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Email</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Yes / No</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Yes / No</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Predefined List</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Free Text (most blank)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Free Text (most blank)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Free Text (most blank)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Yes / No</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Free Text (most blank)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Yes / No</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Free Text (most blank)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">Data Type: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Date</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+          </rPr>
+          <t xml:space="preserve">ENTER MANUALLY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+          </rPr>
+          <t>Type the total number of officers in the pool. Records on Data sheet = submitted only.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>VerificationFormId</t>
-  </si>
-  <si>
-    <t>PtbId</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
+  <si>
+    <t>FormID</t>
+  </si>
+  <si>
+    <t>PTBID</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Last</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>ActiveLe</t>
-  </si>
-  <si>
-    <t>OnLeave</t>
-  </si>
-  <si>
-    <t>TrainingStatus</t>
-  </si>
-  <si>
-    <t>OutOfComplianceExplanation</t>
-  </si>
-  <si>
-    <t>ReasonMandatesNotCompleted</t>
-  </si>
-  <si>
-    <t>EmploymentHistoryExplanation</t>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Mandate Reason</t>
+  </si>
+  <si>
+    <t>Employment Explanation</t>
   </si>
   <si>
     <t>OtherLE</t>
   </si>
   <si>
-    <t>OtherLEExplanation</t>
-  </si>
-  <si>
     <t>Misconduct</t>
   </si>
   <si>
-    <t>MisconductExplanation</t>
-  </si>
-  <si>
-    <t>Submitted</t>
+    <t>Misconduct Explanation</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Numeric ID</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Yes / No</t>
+  </si>
+  <si>
+    <t>Predefined List</t>
+  </si>
+  <si>
+    <t>Free Text (most blank)</t>
   </si>
   <si>
     <t>Officer Verification Dashboard</t>
   </si>
   <si>
-    <t>Auto-updates when new data is pasted into the Data sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Overview</t>
+    <t>All metrics auto-update when data is pasted into the Data sheet (starting row 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Population &amp; Submission Summary</t>
+  </si>
+  <si>
+    <t>Total Officer Population</t>
+  </si>
+  <si>
+    <t>Records in Data (Submitted)</t>
+  </si>
+  <si>
+    <t>Not Yet Submitted</t>
+  </si>
+  <si>
+    <t>Submission Rate (of population)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Officer Status Counts</t>
   </si>
   <si>
     <t xml:space="preserve">  Compliance &amp; Attention Flags</t>
   </si>
   <si>
-    <t>Total Officer Records</t>
+    <t>Active = Yes</t>
   </si>
   <si>
     <t>Misconduct = Yes</t>
   </si>
   <si>
-    <t>Total Submitted</t>
-  </si>
-  <si>
-    <t>Misconduct = Yes AND Submitted = Yes</t>
-  </si>
-  <si>
-    <t>Total Not Submitted</t>
+    <t>Active = No</t>
+  </si>
+  <si>
+    <t>Misconduct = Yes AND has Date</t>
+  </si>
+  <si>
+    <t>Leave = Yes</t>
+  </si>
+  <si>
+    <t>Active = Yes AND Misconduct = Yes</t>
+  </si>
+  <si>
+    <t>Leave = No</t>
+  </si>
+  <si>
+    <t>OtherLE = Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Explanation Fields Populated</t>
+  </si>
+  <si>
+    <t>OtherLE = No</t>
+  </si>
+  <si>
+    <t>Explanation [col I] (non-blank)</t>
+  </si>
+  <si>
+    <t>Mandate Reason (non-blank)</t>
   </si>
   <si>
     <t>Misconduct = No</t>
   </si>
   <si>
-    <t>Submission Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Explanation Fields Populated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Officer Status Counts</t>
-  </si>
-  <si>
-    <t>OutOfComplianceExplanation (non-blank)</t>
-  </si>
-  <si>
-    <t>ActiveLe = Yes</t>
-  </si>
-  <si>
-    <t>ReasonMandatesNotCompleted (non-blank)</t>
-  </si>
-  <si>
-    <t>ActiveLe = No</t>
-  </si>
-  <si>
-    <t>EmploymentHistoryExplanation (non-blank)</t>
-  </si>
-  <si>
-    <t>OnLeave = Yes</t>
-  </si>
-  <si>
-    <t>OtherLEExplanation (non-blank)</t>
-  </si>
-  <si>
-    <t>OnLeave = No</t>
-  </si>
-  <si>
-    <t>MisconductExplanation (non-blank)</t>
-  </si>
-  <si>
-    <t>OtherLE = Yes</t>
-  </si>
-  <si>
-    <t>OtherLE = No</t>
+    <t>Employment Explanation (non-blank)</t>
+  </si>
+  <si>
+    <t>OtherLE Explanation [col M] (non-blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Status Breakdown</t>
+  </si>
+  <si>
+    <t>Misconduct Explanation (non-blank)</t>
+  </si>
+  <si>
+    <t>Compliant</t>
+  </si>
+  <si>
+    <t>Non-Compliant</t>
   </si>
   <si>
     <t xml:space="preserve">  Quick Cross-Tabs</t>
   </si>
   <si>
-    <t>ActiveLe=Yes AND Submitted=Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Training Status Breakdown</t>
-  </si>
-  <si>
-    <t>ActiveLe=Yes AND Submitted=No</t>
-  </si>
-  <si>
-    <t>Training: Compliant</t>
-  </si>
-  <si>
-    <t>OnLeave=Yes AND Submitted=Yes</t>
-  </si>
-  <si>
-    <t>Training: Non-Compliant</t>
-  </si>
-  <si>
-    <t>OnLeave=Yes AND Submitted=No</t>
-  </si>
-  <si>
-    <t>Training: In Progress</t>
-  </si>
-  <si>
-    <t>OtherLE=Yes AND Submitted=Yes</t>
-  </si>
-  <si>
-    <t>Training: Expired</t>
-  </si>
-  <si>
-    <t>OtherLE=Yes AND Submitted=No</t>
-  </si>
-  <si>
-    <t>Training: Exempt</t>
-  </si>
-  <si>
-    <t>Training: Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Notes</t>
-  </si>
-  <si>
-    <t>Training: Not Started</t>
-  </si>
-  <si>
-    <t>Training Status breakdown uses common values. If your data uses different labels, the "Other values" row will catch them — check the Data sheet for actual values and adjust as needed.</t>
-  </si>
-  <si>
-    <t>Training: (Other values)</t>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Active = Yes AND Leave = Yes</t>
+  </si>
+  <si>
+    <t>Expired</t>
+  </si>
+  <si>
+    <t>Active = Yes AND OtherLE = Yes</t>
+  </si>
+  <si>
+    <t>Exempt</t>
+  </si>
+  <si>
+    <t>Leave = Yes AND Misconduct = Yes</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Column Reference</t>
+  </si>
+  <si>
+    <t>(Other / unlisted values)</t>
+  </si>
+  <si>
+    <t>A: FormID</t>
+  </si>
+  <si>
+    <t>B: PTBID</t>
+  </si>
+  <si>
+    <t>C–D: First / Last</t>
+  </si>
+  <si>
+    <t>E: Email</t>
+  </si>
+  <si>
+    <t>Email address</t>
+  </si>
+  <si>
+    <t>F: Active</t>
+  </si>
+  <si>
+    <t>G: Leave</t>
+  </si>
+  <si>
+    <t>H: Status</t>
+  </si>
+  <si>
+    <t>Predefined list</t>
+  </si>
+  <si>
+    <t>I: Explanation</t>
+  </si>
+  <si>
+    <t>Free text (compliance)</t>
+  </si>
+  <si>
+    <t>J: Mandate Reason</t>
+  </si>
+  <si>
+    <t>Free text</t>
+  </si>
+  <si>
+    <t>K: Employment Explanation</t>
+  </si>
+  <si>
+    <t>L: OtherLE</t>
+  </si>
+  <si>
+    <t>M: Explanation</t>
+  </si>
+  <si>
+    <t>Free text (OtherLE)</t>
+  </si>
+  <si>
+    <t>N: Misconduct</t>
+  </si>
+  <si>
+    <t>O: Misconduct Explanation</t>
+  </si>
+  <si>
+    <t>P: Date</t>
+  </si>
+  <si>
+    <t>Date submitted</t>
+  </si>
+  <si>
+    <t>Notes: Row 2 on the Data sheet describes each column's data type. Paste officer records starting at row 3. Status breakdown uses common values — check "Other / unlisted" row if your labels differ. Enter Total Officer Population manually in the blue box above (C7).</t>
   </si>
 </sst>
 </file>
@@ -195,7 +574,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -207,6 +586,11 @@
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -224,6 +608,30 @@
       <sz val="13"/>
     </font>
     <font>
+      <b/>
+      <color rgb="1F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="1F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="1F4E79"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
     <font>
@@ -236,12 +644,20 @@
       <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <i/>
       <color rgb="808080"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,11 +671,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -278,6 +704,21 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color rgb="D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="4472C4"/>
+      </left>
+      <right style="medium">
+        <color rgb="4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="4472C4"/>
+      </top>
       <bottom style="medium">
         <color rgb="4472C4"/>
       </bottom>
@@ -296,33 +737,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -667,21 +1132,21 @@
   <sheetPr>
     <tabColor rgb="4472C4"/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="11" width="30" customWidth="1"/>
+    <col min="9" max="11" width="28" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -722,22 +1187,73 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -746,326 +1262,445 @@
   <sheetPr>
     <tabColor rgb="70AD47"/>
   </sheetPr>
-  <dimension ref="B2:F28"/>
+  <dimension ref="B2:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="6">
-        <f>COUNTA(Data!A:A)-1</f>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="36" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="E7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="8">
+        <f>COUNTA(Data!A:A)-2</f>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="10">
+        <f>IF(C7="","—",C7-(COUNTA(Data!A:A)-2))</f>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="11">
+        <f>IF(OR(C7="",C7=0),0,(COUNTA(Data!A:A)-2)/C7)</f>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="13">
+        <f>COUNTIF(Data!F:F,"Yes")</f>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
         <f>COUNTIF(Data!N:N,"Yes")</f>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6">
-        <f>COUNTIF(Data!P:P,"Yes")</f>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="7">
-        <f>COUNTIFS(Data!N:N,"Yes",Data!P:P,"Yes")</f>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="6">
-        <f>COUNTIF(Data!P:P,"No")</f>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="6">
-        <f>COUNTIF(Data!N:N,"No")</f>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="8">
-        <f>IF(COUNTA(Data!A:A)-1=0,0,COUNTIF(Data!P:P,"Yes")/(COUNTA(Data!A:A)-1))</f>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="E11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="6">
-        <f>COUNTA(Data!I2:I1048576)</f>
-      </c>
-    </row>
     <row r="12" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="6">
-        <f>COUNTIF(Data!F:F,"Yes")</f>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="6">
-        <f>COUNTA(Data!J2:J1048576)</f>
+      <c r="C12" s="13">
+        <f>COUNTIF(Data!F:F,"No")</f>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="14">
+        <f>COUNTIFS(Data!N:N,"Yes",Data!P:P,"&lt;&gt;")</f>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="6">
-        <f>COUNTIF(Data!F:F,"No")</f>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="B13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="6">
-        <f>COUNTA(Data!K2:K1048576)</f>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+      <c r="C13" s="13">
+        <f>COUNTIF(Data!G:G,"Yes")</f>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="6">
-        <f>COUNTIF(Data!G:G,"Yes")</f>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F13" s="14">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!N:N,"Yes")</f>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="6">
-        <f>COUNTA(Data!M2:M1048576)</f>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+      <c r="C14" s="13">
+        <f>COUNTIF(Data!G:G,"No")</f>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="6">
-        <f>COUNTIF(Data!G:G,"No")</f>
+      <c r="C15" s="13">
+        <f>COUNTIF(Data!L:L,"Yes")</f>
       </c>
       <c r="E15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="6">
-        <f>COUNTA(Data!O2:O1048576)</f>
-      </c>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6">
-        <f>COUNTIF(Data!L:L,"Yes")</f>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="C16" s="13">
+        <f>COUNTIF(Data!L:L,"No")</f>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="6">
-        <f>COUNTIF(Data!L:L,"No")</f>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="F16" s="13">
+        <f>COUNTA(Data!I3:I1048576)</f>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="14">
+        <f>COUNTIF(Data!N:N,"Yes")</f>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="13">
+        <f>COUNTA(Data!J3:J1048576)</f>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E18" s="5" t="s">
+      <c r="B18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="6">
-        <f>COUNTIFS(Data!F:F,"Yes",Data!P:P,"Yes")</f>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="13">
+        <f>COUNTIF(Data!N:N,"No")</f>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="E19" s="5" t="s">
+      <c r="F18" s="13">
+        <f>COUNTA(Data!K3:K1048576)</f>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="6">
-        <f>COUNTIFS(Data!F:F,"Yes",Data!P:P,"No")</f>
+      <c r="F19" s="13">
+        <f>COUNTA(Data!M3:M1048576)</f>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5"/>
+      <c r="E20" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="13">
+        <f>COUNTA(Data!O3:O1048576)</f>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="13">
         <f>COUNTIF(Data!H:H,"Compliant")</f>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="6">
-        <f>COUNTIFS(Data!G:G,"Yes",Data!P:P,"Yes")</f>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="6">
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="13">
         <f>COUNTIF(Data!H:H,"Non-Compliant")</f>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="6">
-        <f>COUNTIFS(Data!G:G,"Yes",Data!P:P,"No")</f>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="6">
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="13">
         <f>COUNTIF(Data!H:H,"In Progress")</f>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="6">
-        <f>COUNTIFS(Data!L:L,"Yes",Data!P:P,"Yes")</f>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+      <c r="E23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="6">
+      <c r="F23" s="13">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!G:G,"Yes")</f>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="13">
         <f>COUNTIF(Data!H:H,"Expired")</f>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="6">
-        <f>COUNTIFS(Data!L:L,"Yes",Data!P:P,"No")</f>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+      <c r="E24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="6">
+      <c r="F24" s="13">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!L:L,"Yes")</f>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="13">
         <f>COUNTIF(Data!H:H,"Exempt")</f>
       </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="E25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="13">
+        <f>COUNTIFS(Data!G:G,"Yes",Data!N:N,"Yes")</f>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="13">
         <f>COUNTIF(Data!H:H,"Pending")</f>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="6">
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="13">
         <f>COUNTIF(Data!H:H,"Not Started")</f>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="6">
-        <f>MAX(0, COUNTA(Data!H2:H1048576) - (COUNTIF(Data!H:H,"Compliant")+COUNTIF(Data!H:H,"Non-Compliant")+COUNTIF(Data!H:H,"In Progress")+COUNTIF(Data!H:H,"Expired")+COUNTIF(Data!H:H,"Exempt")+COUNTIF(Data!H:H,"Pending")+COUNTIF(Data!H:H,"Not Started")))</f>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="13">
+        <f>MAX(0, COUNTA(Data!H3:H1048576) - (COUNTIF(Data!H:H,"Compliant")+COUNTIF(Data!H:H,"Non-Compliant")+COUNTIF(Data!H:H,"In Progress")+COUNTIF(Data!H:H,"Expired")+COUNTIF(Data!H:H,"Exempt")+COUNTIF(Data!H:H,"Pending")+COUNTIF(Data!H:H,"Not Started")))</f>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E29" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E30" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E31" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E32" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E34" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E35" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E36" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E38" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E39" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E40" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E41" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F28"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B44:F45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Verification/Officer_Verification_Dashboard.xlsx
+++ b/Verification/Officer_Verification_Dashboard.xlsx
@@ -23,12 +23,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Numeric ID</t>
         </r>
@@ -40,12 +42,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Numeric ID</t>
         </r>
@@ -57,12 +61,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Text</t>
         </r>
@@ -74,12 +80,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Text</t>
         </r>
@@ -91,12 +99,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Email</t>
         </r>
@@ -108,12 +118,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Yes / No</t>
         </r>
@@ -125,12 +137,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Yes / No</t>
         </r>
@@ -142,14 +156,16 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
-          </rPr>
-          <t>Predefined List</t>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>Predefined List (4 values)</t>
         </r>
       </text>
     </comment>
@@ -159,12 +175,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Free Text (most blank)</t>
         </r>
@@ -176,12 +194,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Free Text (most blank)</t>
         </r>
@@ -193,12 +213,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Free Text (most blank)</t>
         </r>
@@ -210,12 +232,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Yes / No</t>
         </r>
@@ -227,12 +251,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Free Text (most blank)</t>
         </r>
@@ -244,12 +270,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Yes / No</t>
         </r>
@@ -261,12 +289,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Free Text (most blank)</t>
         </r>
@@ -278,12 +308,14 @@
           <rPr>
             <b/>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t xml:space="preserve">Data Type: </t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>Date</t>
         </r>
@@ -313,7 +345,8 @@
           <rPr>
             <sz val="9"/>
           </rPr>
-          <t>Type the total number of officers in the pool. Records on Data sheet = submitted only.</t>
+          <t xml:space="preserve">Total officers in the pool.
+Records on Data = submitted only.</t>
         </r>
       </text>
     </comment>
@@ -322,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
   <si>
     <t>FormID</t>
   </si>
@@ -378,7 +411,7 @@
     <t>Yes / No</t>
   </si>
   <si>
-    <t>Predefined List</t>
+    <t>Predefined List (4 values)</t>
   </si>
   <si>
     <t>Free Text (most blank)</t>
@@ -387,10 +420,10 @@
     <t>Officer Verification Dashboard</t>
   </si>
   <si>
-    <t>All metrics auto-update when data is pasted into the Data sheet (starting row 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Population &amp; Submission Summary</t>
+    <t>Metrics update automatically. Paste data on Data sheet starting row 3, or link a CSV (see instructions below).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Population &amp; Submission</t>
   </si>
   <si>
     <t>Total Officer Population</t>
@@ -402,169 +435,196 @@
     <t>Not Yet Submitted</t>
   </si>
   <si>
-    <t>Submission Rate (of population)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Officer Status Counts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Compliance &amp; Attention Flags</t>
+    <t>Submission Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Verification Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cross-Tab Analysis</t>
+  </si>
+  <si>
+    <t>Yes – Completed All Trainings</t>
+  </si>
+  <si>
+    <t>Active AND Completed All</t>
+  </si>
+  <si>
+    <t>No – Will Not Complete (inactivation)</t>
+  </si>
+  <si>
+    <t>Active AND Will Not Complete</t>
+  </si>
+  <si>
+    <t>No – Extension Waiver Granted</t>
+  </si>
+  <si>
+    <t>Active AND Extension Waiver</t>
+  </si>
+  <si>
+    <t>No – Grace Period Requested</t>
+  </si>
+  <si>
+    <t>Active AND Grace Period</t>
+  </si>
+  <si>
+    <t>Active AND Misconduct = Yes</t>
+  </si>
+  <si>
+    <t>Total with Status value</t>
+  </si>
+  <si>
+    <t>Leave AND Completed All</t>
+  </si>
+  <si>
+    <t>Leave AND Will Not Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Officer Flags</t>
+  </si>
+  <si>
+    <t>OtherLE AND Misconduct = Yes</t>
   </si>
   <si>
     <t>Active = Yes</t>
   </si>
   <si>
+    <t>Misconduct = Yes AND Completed All</t>
+  </si>
+  <si>
+    <t>Active = No</t>
+  </si>
+  <si>
+    <t>Misconduct = Yes AND Will Not Complete</t>
+  </si>
+  <si>
+    <t>Leave = Yes</t>
+  </si>
+  <si>
+    <t>Leave = No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Explanation Fields Populated</t>
+  </si>
+  <si>
+    <t>OtherLE = Yes</t>
+  </si>
+  <si>
+    <t>Explanation [col I]  (non-blank)</t>
+  </si>
+  <si>
+    <t>OtherLE = No</t>
+  </si>
+  <si>
+    <t>Mandate Reason [col J]  (non-blank)</t>
+  </si>
+  <si>
     <t>Misconduct = Yes</t>
   </si>
   <si>
-    <t>Active = No</t>
-  </si>
-  <si>
-    <t>Misconduct = Yes AND has Date</t>
-  </si>
-  <si>
-    <t>Leave = Yes</t>
-  </si>
-  <si>
-    <t>Active = Yes AND Misconduct = Yes</t>
-  </si>
-  <si>
-    <t>Leave = No</t>
-  </si>
-  <si>
-    <t>OtherLE = Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Explanation Fields Populated</t>
-  </si>
-  <si>
-    <t>OtherLE = No</t>
-  </si>
-  <si>
-    <t>Explanation [col I] (non-blank)</t>
-  </si>
-  <si>
-    <t>Mandate Reason (non-blank)</t>
+    <t>Employment Explanation [col K]  (non-blank)</t>
   </si>
   <si>
     <t>Misconduct = No</t>
   </si>
   <si>
-    <t>Employment Explanation (non-blank)</t>
-  </si>
-  <si>
-    <t>OtherLE Explanation [col M] (non-blank)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Status Breakdown</t>
-  </si>
-  <si>
-    <t>Misconduct Explanation (non-blank)</t>
-  </si>
-  <si>
-    <t>Compliant</t>
-  </si>
-  <si>
-    <t>Non-Compliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Quick Cross-Tabs</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Active = Yes AND Leave = Yes</t>
-  </si>
-  <si>
-    <t>Expired</t>
-  </si>
-  <si>
-    <t>Active = Yes AND OtherLE = Yes</t>
-  </si>
-  <si>
-    <t>Exempt</t>
-  </si>
-  <si>
-    <t>Leave = Yes AND Misconduct = Yes</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Not Started</t>
+    <t>OtherLE Explanation [col M]  (non-blank)</t>
+  </si>
+  <si>
+    <t>Misconduct Explanation [col O]  (non-blank)</t>
   </si>
   <si>
     <t xml:space="preserve">  Column Reference</t>
   </si>
   <si>
-    <t>(Other / unlisted values)</t>
-  </si>
-  <si>
-    <t>A: FormID</t>
-  </si>
-  <si>
-    <t>B: PTBID</t>
-  </si>
-  <si>
-    <t>C–D: First / Last</t>
-  </si>
-  <si>
-    <t>E: Email</t>
-  </si>
-  <si>
-    <t>Email address</t>
-  </si>
-  <si>
-    <t>F: Active</t>
-  </si>
-  <si>
-    <t>G: Leave</t>
-  </si>
-  <si>
-    <t>H: Status</t>
-  </si>
-  <si>
-    <t>Predefined list</t>
-  </si>
-  <si>
-    <t>I: Explanation</t>
+    <t>A  FormID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  How to Link a CSV File</t>
+  </si>
+  <si>
+    <t>B  PTBID</t>
+  </si>
+  <si>
+    <t>1.  Open this workbook in Excel.</t>
+  </si>
+  <si>
+    <t>C  First  /  D  Last</t>
+  </si>
+  <si>
+    <t>2.  Go to the Data tab → Get Data → From File → From Text/CSV.</t>
+  </si>
+  <si>
+    <t>E  Email</t>
+  </si>
+  <si>
+    <t>3.  Select your downloaded CSV file and click Import.</t>
+  </si>
+  <si>
+    <t>F  Active</t>
+  </si>
+  <si>
+    <t>4.  In the dialog, click Load To… → Existing worksheet.</t>
+  </si>
+  <si>
+    <t>G  Leave</t>
+  </si>
+  <si>
+    <t>5.  Pick cell A1 on the Data sheet, then click OK.</t>
+  </si>
+  <si>
+    <t>H  Status</t>
+  </si>
+  <si>
+    <t>4 predefined values</t>
+  </si>
+  <si>
+    <t>6.  To refresh later: Data tab → Refresh All (or Ctrl+Alt+F5).</t>
+  </si>
+  <si>
+    <t>I  Explanation</t>
   </si>
   <si>
     <t>Free text (compliance)</t>
   </si>
   <si>
-    <t>J: Mandate Reason</t>
+    <t/>
+  </si>
+  <si>
+    <t>J  Mandate Reason</t>
   </si>
   <si>
     <t>Free text</t>
   </si>
   <si>
-    <t>K: Employment Explanation</t>
-  </si>
-  <si>
-    <t>L: OtherLE</t>
-  </si>
-  <si>
-    <t>M: Explanation</t>
+    <t>The CSV must have the same 16 columns in the same order.</t>
+  </si>
+  <si>
+    <t>K  Employment Explanation</t>
+  </si>
+  <si>
+    <t>Row 2 (type descriptors) will be pushed down automatically.</t>
+  </si>
+  <si>
+    <t>L  OtherLE</t>
+  </si>
+  <si>
+    <t>M  Explanation</t>
   </si>
   <si>
     <t>Free text (OtherLE)</t>
   </si>
   <si>
-    <t>N: Misconduct</t>
-  </si>
-  <si>
-    <t>O: Misconduct Explanation</t>
-  </si>
-  <si>
-    <t>P: Date</t>
+    <t>N  Misconduct</t>
+  </si>
+  <si>
+    <t>O  Misconduct Explanation</t>
+  </si>
+  <si>
+    <t>P  Date</t>
   </si>
   <si>
     <t>Date submitted</t>
-  </si>
-  <si>
-    <t>Notes: Row 2 on the Data sheet describes each column's data type. Paste officer records starting at row 3. Status breakdown uses common values — check "Other / unlisted" row if your labels differ. Enter Total Officer Population manually in the blue box above (C7).</t>
   </si>
 </sst>
 </file>
@@ -574,7 +634,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -586,78 +646,109 @@
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="666666"/>
+      <color rgb="595959"/>
       <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="1F4E79"/>
-      <sz val="16"/>
+      <color rgb="1F3864"/>
+      <sz val="18"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="808080"/>
       <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="1F4E79"/>
+      <color rgb="1F3864"/>
       <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="1F4E79"/>
-      <sz val="14"/>
+      <color rgb="1F3864"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="1F4E79"/>
-      <sz val="18"/>
+      <color rgb="548235"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="404040"/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="C00000"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="1F3864"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="404040"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="548235"/>
       <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="C00000"/>
       <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <color rgb="BF8F00"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="666666"/>
+      <b/>
+      <color rgb="404040"/>
       <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
       <color rgb="808080"/>
       <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="404040"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,12 +757,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="4472C4"/>
+        <fgColor rgb="2F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="F2F2F2"/>
+        <fgColor rgb="E9EDF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -681,11 +772,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -694,33 +795,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="1F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="1F3864"/>
+      </top>
       <bottom style="thin">
-        <color rgb="D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="4472C4"/>
-      </left>
-      <right style="medium">
-        <color rgb="4472C4"/>
-      </right>
-      <top style="medium">
-        <color rgb="4472C4"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="4472C4"/>
+        <color rgb="1F3864"/>
       </bottom>
       <diagonal/>
     </border>
@@ -729,7 +814,97 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="D9E2F3"/>
+        <color rgb="B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="4472C4"/>
+      </left>
+      <right style="thin">
+        <color rgb="4472C4"/>
+      </right>
+      <top style="thin">
+        <color rgb="4472C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="548235"/>
+      </left>
+      <right style="thin">
+        <color rgb="548235"/>
+      </right>
+      <top style="thin">
+        <color rgb="548235"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="548235"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="C00000"/>
+      </left>
+      <right style="thin">
+        <color rgb="C00000"/>
+      </right>
+      <top style="thin">
+        <color rgb="C00000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="C00000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="E2EFDA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="D6E4F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FCE4EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFF2CC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -745,50 +920,74 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,13 +1338,12 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="11" width="28" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1199,7 +1397,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1261,20 +1459,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="70AD47"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F45"/>
+  <dimension ref="B2:F43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="32" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="36" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
@@ -1283,7 +1482,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
@@ -1292,7 +1491,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
@@ -1301,8 +1500,8 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="36" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="38" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
@@ -1314,7 +1513,7 @@
         <f>COUNTA(Data!A:A)-2</f>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
@@ -1328,7 +1527,8 @@
         <f>IF(OR(C7="",C7=0),0,(COUNTA(Data!A:A)-2)/C7)</f>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>27</v>
       </c>
@@ -1343,364 +1543,400 @@
         <v>29</v>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIF(Data!F:F,"Yes")</f>
+        <f>COUNTIF(Data!H:H,"Yes*")</f>
       </c>
       <c r="E11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="14">
-        <f>COUNTIF(Data!N:N,"Yes")</f>
+        <f>COUNTIFS(Data!F:F,"Yes",Data!H:H,"Yes*")</f>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="13">
-        <f>COUNTIF(Data!F:F,"No")</f>
+      <c r="C12" s="15">
+        <f>COUNTIF(Data!H:H,"No – I do not plan*")</f>
       </c>
       <c r="E12" s="12" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="14">
-        <f>COUNTIFS(Data!N:N,"Yes",Data!P:P,"&lt;&gt;")</f>
+        <f>COUNTIFS(Data!F:F,"Yes",Data!H:H,"No – I do not plan*")</f>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="13">
-        <f>COUNTIF(Data!G:G,"Yes")</f>
+      <c r="C13" s="16">
+        <f>COUNTIF(Data!H:H,"No – I have been granted*")</f>
       </c>
       <c r="E13" s="12" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="14">
-        <f>COUNTIFS(Data!F:F,"Yes",Data!N:N,"Yes")</f>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!H:H,"No – I have been granted*")</f>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="13">
-        <f>COUNTIF(Data!G:G,"No")</f>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+      <c r="C14" s="16">
+        <f>COUNTIF(Data!H:H,"No – I require*")</f>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="13">
-        <f>COUNTIF(Data!L:L,"Yes")</f>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="F14" s="14">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!H:H,"No – I require*")</f>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="14">
+        <f>COUNTIFS(Data!F:F,"Yes",Data!N:N,"Yes")</f>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="13">
-        <f>COUNTIF(Data!L:L,"No")</f>
+      <c r="C16" s="18">
+        <f>COUNTA(Data!H3:H1048576)</f>
       </c>
       <c r="E16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="13">
-        <f>COUNTA(Data!I3:I1048576)</f>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="14">
-        <f>COUNTIF(Data!N:N,"Yes")</f>
-      </c>
+      <c r="F16" s="14">
+        <f>COUNTIFS(Data!G:G,"Yes",Data!H:H,"Yes*")</f>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="13">
-        <f>COUNTA(Data!J3:J1048576)</f>
+      <c r="F17" s="14">
+        <f>COUNTIFS(Data!G:G,"Yes",Data!H:H,"No – I do not plan*")</f>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="13">
-        <f>COUNTIF(Data!N:N,"No")</f>
-      </c>
+      <c r="C18" s="5"/>
       <c r="E18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="13">
-        <f>COUNTA(Data!K3:K1048576)</f>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="14">
+        <f>COUNTIFS(Data!L:L,"Yes",Data!N:N,"Yes")</f>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="14">
+        <f>COUNTIF(Data!F:F,"Yes")</f>
+      </c>
       <c r="E19" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="13">
-        <f>COUNTA(Data!M3:M1048576)</f>
+        <v>44</v>
+      </c>
+      <c r="F19" s="14">
+        <f>COUNTIFS(Data!N:N,"Yes",Data!H:H,"Yes*")</f>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="5"/>
+      <c r="B20" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="14">
+        <f>COUNTIF(Data!F:F,"No")</f>
+      </c>
       <c r="E20" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="13">
-        <f>COUNTA(Data!O3:O1048576)</f>
+        <v>46</v>
+      </c>
+      <c r="F20" s="14">
+        <f>COUNTIFS(Data!N:N,"Yes",Data!H:H,"No – I do not plan*")</f>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="13">
-        <f>COUNTIF(Data!H:H,"Compliant")</f>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C21" s="14">
+        <f>COUNTIF(Data!G:G,"Yes")</f>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="13">
-        <f>COUNTIF(Data!H:H,"Non-Compliant")</f>
+        <v>48</v>
+      </c>
+      <c r="C22" s="14">
+        <f>COUNTIF(Data!G:G,"No")</f>
       </c>
       <c r="E22" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" s="5"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="13">
-        <f>COUNTIF(Data!H:H,"In Progress")</f>
+        <v>50</v>
+      </c>
+      <c r="C23" s="14">
+        <f>COUNTIF(Data!L:L,"Yes")</f>
       </c>
       <c r="E23" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="13">
-        <f>COUNTIFS(Data!F:F,"Yes",Data!G:G,"Yes")</f>
+        <v>51</v>
+      </c>
+      <c r="F23" s="14">
+        <f>COUNTA(Data!I3:I1048576)</f>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="13">
-        <f>COUNTIF(Data!H:H,"Expired")</f>
+        <v>52</v>
+      </c>
+      <c r="C24" s="14">
+        <f>COUNTIF(Data!L:L,"No")</f>
       </c>
       <c r="E24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="13">
-        <f>COUNTIFS(Data!F:F,"Yes",Data!L:L,"Yes")</f>
+        <v>53</v>
+      </c>
+      <c r="F24" s="14">
+        <f>COUNTA(Data!J3:J1048576)</f>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="13">
-        <f>COUNTIF(Data!H:H,"Exempt")</f>
+        <v>54</v>
+      </c>
+      <c r="C25" s="19">
+        <f>COUNTIF(Data!N:N,"Yes")</f>
       </c>
       <c r="E25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="13">
-        <f>COUNTIFS(Data!G:G,"Yes",Data!N:N,"Yes")</f>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="F25" s="14">
+        <f>COUNTA(Data!K3:K1048576)</f>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="13">
-        <f>COUNTIF(Data!H:H,"Pending")</f>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="13">
-        <f>COUNTIF(Data!H:H,"Not Started")</f>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="C26" s="14">
+        <f>COUNTIF(Data!N:N,"No")</f>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
+      <c r="F26" s="14">
+        <f>COUNTA(Data!M3:M1048576)</f>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="13">
-        <f>MAX(0, COUNTA(Data!H3:H1048576) - (COUNTIF(Data!H:H,"Compliant")+COUNTIF(Data!H:H,"Non-Compliant")+COUNTIF(Data!H:H,"In Progress")+COUNTIF(Data!H:H,"Expired")+COUNTIF(Data!H:H,"Exempt")+COUNTIF(Data!H:H,"Pending")+COUNTIF(Data!H:H,"Not Started")))</f>
-      </c>
-      <c r="E28" s="15" t="s">
+      <c r="F27" s="14">
+        <f>COUNTA(Data!O3:O1048576)</f>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E29" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="16" t="s">
+      <c r="E29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="16" t="s">
+      <c r="E30" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E31" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E32" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="16" t="s">
+      <c r="E31" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="33" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E33" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="16" t="s">
+      <c r="E33" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="23" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E34" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E35" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E36" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="16" t="s">
+      <c r="E34" s="24" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E37" s="15" t="s">
+      <c r="F34" s="24"/>
+    </row>
+    <row r="35" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E38" s="15" t="s">
+      <c r="C35" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="E35" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="24"/>
+    </row>
+    <row r="36" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" s="25"/>
+    </row>
+    <row r="38" ht="16" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="25"/>
+    </row>
+    <row r="39" ht="16" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E39" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E40" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="16" t="s">
+    <row r="40" ht="16" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E41" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E42" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" s="16" t="s">
+    <row r="42" ht="16" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
+    <row r="43" ht="16" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="18">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B44:F45"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>